--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="460" windowWidth="27100" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="1700" yWindow="460" windowWidth="27100" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>TCID</t>
   </si>
@@ -166,9 +166,6 @@
     <t>ProductName</t>
   </si>
   <si>
-    <t>ice-dog-tag-layered-pendant-necklace</t>
-  </si>
-  <si>
     <t>What's New</t>
   </si>
   <si>
@@ -265,10 +262,28 @@
     <t>EarnVaultPointTest</t>
   </si>
   <si>
-    <t>pave-sputnik-ear-jackets-earring</t>
-  </si>
-  <si>
-    <t>VaultPointWithDicountTest</t>
+    <t>CCExpirMonth</t>
+  </si>
+  <si>
+    <t>CCExpirYear</t>
+  </si>
+  <si>
+    <t>starry-avatar-cuff-bracelet</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>bahama-tassel-drops-earrings</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>BBENG</t>
   </si>
   <si>
     <t>VaultPointAmount</t>
@@ -277,7 +292,16 @@
     <t>DiscountCode</t>
   </si>
   <si>
-    <t>BBENG</t>
+    <t>PaginationTest</t>
+  </si>
+  <si>
+    <t>What'sNew</t>
+  </si>
+  <si>
+    <t>VaultPointsWithDicountTest</t>
+  </si>
+  <si>
+    <t>starburst-studs-earrings</t>
   </si>
 </sst>
 </file>
@@ -744,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -869,7 +893,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -877,7 +901,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
         <v>3</v>
@@ -885,7 +909,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
         <v>3</v>
@@ -893,7 +917,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
@@ -901,7 +925,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
@@ -909,7 +933,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
         <v>3</v>
@@ -917,9 +941,17 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
         <v>3</v>
       </c>
     </row>
@@ -931,7 +963,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M98"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -947,6 +979,8 @@
     <col min="11" max="11" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.1640625" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1204,7 +1238,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C47" s="12"/>
     </row>
@@ -1217,7 +1251,7 @@
       </c>
       <c r="C48" s="12"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1260,7 @@
       </c>
       <c r="C49" s="12"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>3</v>
       </c>
@@ -1235,7 +1269,7 @@
       </c>
       <c r="C50" s="12"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>3</v>
       </c>
@@ -1244,7 +1278,7 @@
       </c>
       <c r="C51" s="12"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>3</v>
       </c>
@@ -1252,7 +1286,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>3</v>
       </c>
@@ -1260,7 +1294,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>3</v>
       </c>
@@ -1268,12 +1302,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>2</v>
       </c>
@@ -1284,16 +1318,16 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C58" s="12"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>3</v>
       </c>
@@ -1302,7 +1336,7 @@
       </c>
       <c r="C59" s="12"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1345,7 @@
       </c>
       <c r="C60" s="12"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>3</v>
       </c>
@@ -1319,8 +1353,9 @@
         <v>34</v>
       </c>
       <c r="C61" s="12"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>3</v>
       </c>
@@ -1329,7 +1364,7 @@
       </c>
       <c r="C62" s="12"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>3</v>
       </c>
@@ -1337,7 +1372,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>3</v>
       </c>
@@ -1345,7 +1380,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>3</v>
       </c>
@@ -1353,7 +1388,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>15</v>
       </c>
@@ -1361,12 +1396,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>2</v>
       </c>
@@ -1374,86 +1409,98 @@
         <v>45</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D69" t="s">
         <v>5</v>
       </c>
       <c r="E69" t="s">
+        <v>49</v>
+      </c>
+      <c r="F69" t="s">
+        <v>60</v>
+      </c>
+      <c r="G69" t="s">
+        <v>59</v>
+      </c>
+      <c r="H69" t="s">
         <v>50</v>
       </c>
-      <c r="F69" t="s">
-        <v>61</v>
-      </c>
-      <c r="G69" t="s">
-        <v>60</v>
-      </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>51</v>
       </c>
-      <c r="I69" t="s">
+      <c r="J69" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J69" s="15" t="s">
+      <c r="K69" t="s">
         <v>53</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" t="s">
+        <v>64</v>
+      </c>
+      <c r="M69" t="s">
+        <v>65</v>
+      </c>
+      <c r="N69" t="s">
+        <v>78</v>
+      </c>
+      <c r="O69" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" ht="18" x14ac:dyDescent="0.2">
+      <c r="A70" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" t="s">
         <v>54</v>
-      </c>
-      <c r="L69" t="s">
-        <v>65</v>
-      </c>
-      <c r="M69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="18" x14ac:dyDescent="0.2">
-      <c r="A70" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C70" t="s">
-        <v>55</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="E70" t="s">
+        <v>55</v>
+      </c>
+      <c r="F70" t="s">
         <v>56</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>57</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>58</v>
       </c>
-      <c r="H70" t="s">
-        <v>59</v>
-      </c>
       <c r="I70" t="s">
+        <v>61</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="K70" t="s">
         <v>62</v>
       </c>
-      <c r="J70" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="K70" t="s">
-        <v>63</v>
-      </c>
       <c r="L70" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="M70" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>2</v>
       </c>
@@ -1461,32 +1508,32 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A80" s="11" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A80" s="11" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -1494,7 +1541,7 @@
         <v>2</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
@@ -1502,12 +1549,12 @@
         <v>3</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -1523,12 +1570,12 @@
         <v>3</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
@@ -1544,12 +1591,12 @@
         <v>3</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
@@ -1565,16 +1612,16 @@
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>80</v>
+      <c r="A96" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" s="12" t="s">
+      <c r="A97" t="s">
         <v>2</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -1587,18 +1634,18 @@
         <v>5</v>
       </c>
       <c r="E97" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F97" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="12" t="s">
+      <c r="A98" t="s">
         <v>3</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>17</v>
@@ -1606,11 +1653,88 @@
       <c r="D98" t="s">
         <v>18</v>
       </c>
-      <c r="E98">
-        <v>1</v>
+      <c r="E98" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="F98" t="s">
-        <v>83</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="98">
   <si>
     <t>TCID</t>
   </si>
@@ -277,9 +277,6 @@
     <t>2017</t>
   </si>
   <si>
-    <t>bahama-tassel-drops-earrings</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -295,13 +292,34 @@
     <t>PaginationTest</t>
   </si>
   <si>
-    <t>What'sNew</t>
-  </si>
-  <si>
     <t>VaultPointsWithDicountTest</t>
   </si>
   <si>
     <t>starburst-studs-earrings</t>
+  </si>
+  <si>
+    <t>necklaces</t>
+  </si>
+  <si>
+    <t>earrings</t>
+  </si>
+  <si>
+    <t>bracelets</t>
+  </si>
+  <si>
+    <t>rings</t>
+  </si>
+  <si>
+    <t>personalized</t>
+  </si>
+  <si>
+    <t>whats-new/just-added</t>
+  </si>
+  <si>
+    <t>RemoveItemTest</t>
+  </si>
+  <si>
+    <t>pave-droplet-ear-crawlers-earrings</t>
   </si>
 </sst>
 </file>
@@ -768,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -941,7 +959,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -949,9 +967,17 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="s">
         <v>3</v>
       </c>
     </row>
@@ -963,7 +989,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -1256,7 +1282,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C49" s="12"/>
     </row>
@@ -1265,7 +1291,7 @@
         <v>3</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C50" s="12"/>
     </row>
@@ -1341,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C60" s="12"/>
     </row>
@@ -1350,7 +1376,7 @@
         <v>3</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" s="12"/>
       <c r="O61" s="3"/>
@@ -1382,7 +1408,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>38</v>
@@ -1612,15 +1638,15 @@
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>2</v>
       </c>
@@ -1634,18 +1660,18 @@
         <v>5</v>
       </c>
       <c r="E97" t="s">
+        <v>85</v>
+      </c>
+      <c r="F97" t="s">
         <v>86</v>
       </c>
-      <c r="F97" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>3</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>17</v>
@@ -1654,18 +1680,18 @@
         <v>18</v>
       </c>
       <c r="E98" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F98" t="s">
         <v>84</v>
       </c>
-      <c r="F98" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>2</v>
       </c>
@@ -1673,68 +1699,83 @@
         <v>40</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>3</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>3</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>3</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>3</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>3</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>3</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
-        <v>3</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B108"/>
+      <c r="I108" s="15"/>
+      <c r="J108"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>3</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>38</v>
+        <v>96</v>
+      </c>
+      <c r="B109"/>
+      <c r="I109" s="15"/>
+      <c r="J109"/>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>2</v>
+      </c>
+      <c r="B110" t="s">
+        <v>45</v>
+      </c>
+      <c r="I110" s="15"/>
+      <c r="J110"/>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>3</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="25007"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="26311"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rumanaafroz/Automation/BaublebarTest/src/com/baublebar/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="200" windowWidth="27100" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="1700" yWindow="460" windowWidth="27100" windowHeight="15820"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -21,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>TCID</t>
   </si>
@@ -267,6 +272,36 @@
   </si>
   <si>
     <t>starry-avatar-cuff-bracelet</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>VaultPointsWithDiscountTest</t>
+  </si>
+  <si>
+    <t>bahama-tassel-drops-earrings</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>BBENG</t>
+  </si>
+  <si>
+    <t>VaultPointAmount</t>
+  </si>
+  <si>
+    <t>DiscountCode</t>
+  </si>
+  <si>
+    <t>PaginationTest</t>
+  </si>
+  <si>
+    <t>What'sNew</t>
   </si>
 </sst>
 </file>
@@ -440,6 +475,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -728,14 +768,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
@@ -755,7 +795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -763,7 +803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -771,7 +811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -779,7 +819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -787,7 +827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -795,7 +835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -803,7 +843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -811,7 +851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -819,7 +859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -827,7 +867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -835,7 +875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -843,7 +883,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -851,7 +891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -859,7 +899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -867,7 +907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -875,7 +915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -883,7 +923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -891,29 +931,40 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>77</v>
       </c>
       <c r="C20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:O109"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" style="3" customWidth="1"/>
@@ -929,29 +980,30 @@
     <col min="12" max="12" width="20.1640625" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" customWidth="1"/>
     <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -959,7 +1011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -967,12 +1019,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -983,7 +1035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -994,12 +1046,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>2</v>
       </c>
@@ -1010,7 +1062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1021,61 +1073,61 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
@@ -1086,7 +1138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1097,27 +1149,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -1125,7 +1177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1185,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1141,7 +1193,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1209,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1165,14 +1217,14 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12"/>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>2</v>
       </c>
@@ -1181,7 +1233,7 @@
       </c>
       <c r="C46" s="12"/>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +1242,7 @@
       </c>
       <c r="C47" s="12"/>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1251,7 @@
       </c>
       <c r="C48" s="12"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>3</v>
       </c>
@@ -1208,7 +1260,7 @@
       </c>
       <c r="C49" s="12"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>3</v>
       </c>
@@ -1217,7 +1269,7 @@
       </c>
       <c r="C50" s="12"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1278,7 @@
       </c>
       <c r="C51" s="12"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1286,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>3</v>
       </c>
@@ -1242,7 +1294,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>3</v>
       </c>
@@ -1250,12 +1302,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>2</v>
       </c>
@@ -1266,7 +1318,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>3</v>
       </c>
@@ -1275,7 +1327,7 @@
       </c>
       <c r="C58" s="12"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1336,7 @@
       </c>
       <c r="C59" s="12"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>3</v>
       </c>
@@ -1293,7 +1345,7 @@
       </c>
       <c r="C60" s="12"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>3</v>
       </c>
@@ -1301,8 +1353,9 @@
         <v>34</v>
       </c>
       <c r="C61" s="12"/>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1364,7 @@
       </c>
       <c r="C62" s="12"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>3</v>
       </c>
@@ -1319,7 +1372,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>3</v>
       </c>
@@ -1327,7 +1380,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>3</v>
       </c>
@@ -1335,7 +1388,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>15</v>
       </c>
@@ -1343,12 +1396,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>2</v>
       </c>
@@ -1395,7 +1448,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="17">
+    <row r="70" spans="1:15" ht="18" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>3</v>
       </c>
@@ -1435,19 +1488,19 @@
       <c r="M70" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N70">
-        <v>12</v>
-      </c>
-      <c r="O70">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15">
+      <c r="N70" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>2</v>
       </c>
@@ -1455,7 +1508,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>3</v>
       </c>
@@ -1463,27 +1516,27 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -1491,7 +1544,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>3</v>
       </c>
@@ -1499,12 +1552,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>2</v>
       </c>
@@ -1512,7 +1565,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="12" t="s">
         <v>3</v>
       </c>
@@ -1520,12 +1573,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="12" t="s">
         <v>2</v>
       </c>
@@ -1533,7 +1586,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="12" t="s">
         <v>3</v>
       </c>
@@ -1541,12 +1594,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="12" t="s">
         <v>2</v>
       </c>
@@ -1554,12 +1607,134 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D97" t="s">
+        <v>5</v>
+      </c>
+      <c r="E97" t="s">
+        <v>88</v>
+      </c>
+      <c r="F97" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F98" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1568,27 +1743,18 @@
     <hyperlink ref="B31" r:id="rId2"/>
     <hyperlink ref="B7" r:id="rId3"/>
     <hyperlink ref="B15" r:id="rId4"/>
+    <hyperlink ref="C98" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="101">
   <si>
     <t>TCID</t>
   </si>
@@ -280,46 +280,55 @@
     <t>1</t>
   </si>
   <si>
+    <t>VaultPointAmount</t>
+  </si>
+  <si>
+    <t>DiscountCode</t>
+  </si>
+  <si>
+    <t>PaginationTest</t>
+  </si>
+  <si>
+    <t>VaultPointsWithDicountTest</t>
+  </si>
+  <si>
+    <t>starburst-studs-earrings</t>
+  </si>
+  <si>
+    <t>necklaces</t>
+  </si>
+  <si>
+    <t>earrings</t>
+  </si>
+  <si>
+    <t>bracelets</t>
+  </si>
+  <si>
+    <t>rings</t>
+  </si>
+  <si>
+    <t>personalized</t>
+  </si>
+  <si>
+    <t>whats-new/just-added</t>
+  </si>
+  <si>
+    <t>pave-droplet-ear-crawlers-earrings</t>
+  </si>
+  <si>
+    <t>ProductName1</t>
+  </si>
+  <si>
+    <t>ProductName2</t>
+  </si>
+  <si>
+    <t>AddItemsTest</t>
+  </si>
+  <si>
+    <t>RemoveItemFromShoppingCartTest</t>
+  </si>
+  <si>
     <t>BBENG</t>
-  </si>
-  <si>
-    <t>VaultPointAmount</t>
-  </si>
-  <si>
-    <t>DiscountCode</t>
-  </si>
-  <si>
-    <t>PaginationTest</t>
-  </si>
-  <si>
-    <t>VaultPointsWithDicountTest</t>
-  </si>
-  <si>
-    <t>starburst-studs-earrings</t>
-  </si>
-  <si>
-    <t>necklaces</t>
-  </si>
-  <si>
-    <t>earrings</t>
-  </si>
-  <si>
-    <t>bracelets</t>
-  </si>
-  <si>
-    <t>rings</t>
-  </si>
-  <si>
-    <t>personalized</t>
-  </si>
-  <si>
-    <t>whats-new/just-added</t>
-  </si>
-  <si>
-    <t>RemoveItemTest</t>
-  </si>
-  <si>
-    <t>pave-droplet-ear-crawlers-earrings</t>
   </si>
 </sst>
 </file>
@@ -786,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -959,7 +968,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -967,7 +976,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -975,9 +984,17 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" t="s">
         <v>3</v>
       </c>
     </row>
@@ -989,12 +1006,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="26.6640625" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
     <col min="5" max="5" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
@@ -1229,7 +1246,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>29</v>
@@ -1638,12 +1655,12 @@
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
@@ -1660,10 +1677,10 @@
         <v>5</v>
       </c>
       <c r="E97" t="s">
+        <v>84</v>
+      </c>
+      <c r="F97" t="s">
         <v>85</v>
-      </c>
-      <c r="F97" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
@@ -1671,7 +1688,7 @@
         <v>3</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>17</v>
@@ -1683,12 +1700,12 @@
         <v>83</v>
       </c>
       <c r="F98" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
@@ -1704,7 +1721,7 @@
         <v>3</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
@@ -1712,7 +1729,7 @@
         <v>3</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
@@ -1720,7 +1737,7 @@
         <v>3</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
@@ -1728,7 +1745,7 @@
         <v>3</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
@@ -1736,7 +1753,7 @@
         <v>3</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -1744,7 +1761,7 @@
         <v>3</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
@@ -1753,8 +1770,8 @@
       <c r="J108"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>96</v>
+      <c r="A109" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="B109"/>
       <c r="I109" s="15"/>
@@ -1775,7 +1792,34 @@
         <v>3</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" s="11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>2</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C114" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C115" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="25007"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="26311"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rumanaafroz/Automation/BaublebarTest/src/com/baublebar/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="200" windowWidth="27100" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="1700" yWindow="460" windowWidth="27100" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -21,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="86">
   <si>
     <t>TCID</t>
   </si>
@@ -267,6 +272,18 @@
   </si>
   <si>
     <t>starry-avatar-cuff-bracelet</t>
+  </si>
+  <si>
+    <t>AddItemsTest</t>
+  </si>
+  <si>
+    <t>ProductName1</t>
+  </si>
+  <si>
+    <t>ProductName2</t>
+  </si>
+  <si>
+    <t>roma-studs-earrings</t>
   </si>
 </sst>
 </file>
@@ -440,6 +457,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -728,14 +750,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
@@ -755,7 +777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -763,7 +785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -771,7 +793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -779,7 +801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -787,7 +809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -795,7 +817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -803,7 +825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -811,7 +833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -819,7 +841,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -827,7 +849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -835,7 +857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -843,7 +865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -851,7 +873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -859,7 +881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -867,7 +889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -875,7 +897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -883,7 +905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -891,29 +913,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>77</v>
       </c>
       <c r="C20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:O98"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" style="3" customWidth="1"/>
@@ -931,27 +956,27 @@
     <col min="14" max="14" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -959,7 +984,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -967,12 +992,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -983,7 +1008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -994,12 +1019,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>2</v>
       </c>
@@ -1010,7 +1035,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1021,61 +1046,61 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
@@ -1086,7 +1111,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1097,27 +1122,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -1125,7 +1150,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1158,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1141,7 +1166,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1182,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1165,14 +1190,14 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12"/>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>2</v>
       </c>
@@ -1181,7 +1206,7 @@
       </c>
       <c r="C46" s="12"/>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +1215,7 @@
       </c>
       <c r="C47" s="12"/>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1224,7 @@
       </c>
       <c r="C48" s="12"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>3</v>
       </c>
@@ -1208,7 +1233,7 @@
       </c>
       <c r="C49" s="12"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>3</v>
       </c>
@@ -1217,7 +1242,7 @@
       </c>
       <c r="C50" s="12"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1251,7 @@
       </c>
       <c r="C51" s="12"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>3</v>
       </c>
@@ -1242,7 +1267,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>3</v>
       </c>
@@ -1250,12 +1275,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>2</v>
       </c>
@@ -1266,7 +1291,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>3</v>
       </c>
@@ -1275,7 +1300,7 @@
       </c>
       <c r="C58" s="12"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1309,7 @@
       </c>
       <c r="C59" s="12"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>3</v>
       </c>
@@ -1293,7 +1318,7 @@
       </c>
       <c r="C60" s="12"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>3</v>
       </c>
@@ -1302,7 +1327,7 @@
       </c>
       <c r="C61" s="12"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1336,7 @@
       </c>
       <c r="C62" s="12"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>3</v>
       </c>
@@ -1319,7 +1344,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>3</v>
       </c>
@@ -1327,7 +1352,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>3</v>
       </c>
@@ -1335,7 +1360,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>15</v>
       </c>
@@ -1343,12 +1368,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>2</v>
       </c>
@@ -1395,7 +1420,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="17">
+    <row r="70" spans="1:15" ht="18" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>3</v>
       </c>
@@ -1442,12 +1467,12 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>2</v>
       </c>
@@ -1455,7 +1480,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>3</v>
       </c>
@@ -1463,27 +1488,27 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -1491,7 +1516,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>3</v>
       </c>
@@ -1499,12 +1524,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>2</v>
       </c>
@@ -1512,7 +1537,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="12" t="s">
         <v>3</v>
       </c>
@@ -1520,12 +1545,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="12" t="s">
         <v>2</v>
       </c>
@@ -1533,7 +1558,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="12" t="s">
         <v>3</v>
       </c>
@@ -1541,12 +1566,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="12" t="s">
         <v>2</v>
       </c>
@@ -1554,12 +1579,39 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C97" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C98" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1571,24 +1623,14 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="25007"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="26311"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rumanaafroz/Automation/BaublebarTest/src/com/baublebar/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="200" windowWidth="27100" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="11300" yWindow="460" windowWidth="27100" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -21,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="84">
   <si>
     <t>TCID</t>
   </si>
@@ -267,6 +272,12 @@
   </si>
   <si>
     <t>starry-avatar-cuff-bracelet</t>
+  </si>
+  <si>
+    <t>RemoveItemFromShoppingCartTest</t>
+  </si>
+  <si>
+    <t>goldenrod-drops-earrings</t>
   </si>
 </sst>
 </file>
@@ -440,6 +451,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -728,14 +744,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
@@ -755,7 +771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -763,7 +779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -771,7 +787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -779,7 +795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -787,7 +803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -795,7 +811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -803,7 +819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -811,7 +827,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -819,7 +835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -827,7 +843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -835,7 +851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -843,7 +859,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -851,7 +867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -859,7 +875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -867,7 +883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -875,7 +891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -883,7 +899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -891,31 +907,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>77</v>
       </c>
       <c r="C20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:O98"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.33203125" customWidth="1"/>
+    <col min="1" max="1" width="27.1640625" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" customWidth="1"/>
@@ -931,27 +950,27 @@
     <col min="14" max="14" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -959,7 +978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -967,12 +986,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -983,7 +1002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -994,12 +1013,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>2</v>
       </c>
@@ -1010,7 +1029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1021,61 +1040,61 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
@@ -1086,7 +1105,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1097,27 +1116,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -1125,7 +1144,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1152,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1141,7 +1160,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1176,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1165,14 +1184,14 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12"/>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>2</v>
       </c>
@@ -1181,7 +1200,7 @@
       </c>
       <c r="C46" s="12"/>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +1209,7 @@
       </c>
       <c r="C47" s="12"/>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1218,7 @@
       </c>
       <c r="C48" s="12"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>3</v>
       </c>
@@ -1208,7 +1227,7 @@
       </c>
       <c r="C49" s="12"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>3</v>
       </c>
@@ -1217,7 +1236,7 @@
       </c>
       <c r="C50" s="12"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1245,7 @@
       </c>
       <c r="C51" s="12"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1253,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>3</v>
       </c>
@@ -1242,7 +1261,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>3</v>
       </c>
@@ -1250,12 +1269,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>2</v>
       </c>
@@ -1266,7 +1285,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>3</v>
       </c>
@@ -1275,7 +1294,7 @@
       </c>
       <c r="C58" s="12"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1303,7 @@
       </c>
       <c r="C59" s="12"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>3</v>
       </c>
@@ -1293,7 +1312,7 @@
       </c>
       <c r="C60" s="12"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>3</v>
       </c>
@@ -1302,7 +1321,7 @@
       </c>
       <c r="C61" s="12"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1330,7 @@
       </c>
       <c r="C62" s="12"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>3</v>
       </c>
@@ -1319,7 +1338,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>3</v>
       </c>
@@ -1327,7 +1346,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>3</v>
       </c>
@@ -1335,7 +1354,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>15</v>
       </c>
@@ -1343,12 +1362,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>2</v>
       </c>
@@ -1395,7 +1414,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="17">
+    <row r="70" spans="1:15" ht="18" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>3</v>
       </c>
@@ -1442,12 +1461,12 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>2</v>
       </c>
@@ -1455,7 +1474,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>3</v>
       </c>
@@ -1463,27 +1482,27 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -1491,7 +1510,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>3</v>
       </c>
@@ -1499,12 +1518,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>2</v>
       </c>
@@ -1512,7 +1531,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="12" t="s">
         <v>3</v>
       </c>
@@ -1520,12 +1539,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="12" t="s">
         <v>2</v>
       </c>
@@ -1533,7 +1552,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="12" t="s">
         <v>3</v>
       </c>
@@ -1541,12 +1560,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="12" t="s">
         <v>2</v>
       </c>
@@ -1554,12 +1573,33 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1571,24 +1611,14 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="25007"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="26311"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rumanaafroz/Automation/BaublebarTest/src/com/baublebar/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="200" windowWidth="27100" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="22760" yWindow="460" windowWidth="15640" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -21,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="89">
   <si>
     <t>TCID</t>
   </si>
@@ -267,6 +272,27 @@
   </si>
   <si>
     <t>starry-avatar-cuff-bracelet</t>
+  </si>
+  <si>
+    <t>PaginationTest</t>
+  </si>
+  <si>
+    <t>whats-new/just-added</t>
+  </si>
+  <si>
+    <t>necklaces</t>
+  </si>
+  <si>
+    <t>earrings</t>
+  </si>
+  <si>
+    <t>bracelets</t>
+  </si>
+  <si>
+    <t>rings</t>
+  </si>
+  <si>
+    <t>personalized/view-all</t>
   </si>
 </sst>
 </file>
@@ -440,6 +466,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -728,14 +759,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
@@ -755,7 +786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -763,7 +794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -771,7 +802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -779,7 +810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -787,7 +818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -795,7 +826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -803,7 +834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -811,7 +842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -819,7 +850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -827,7 +858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -835,7 +866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -843,7 +874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -851,7 +882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -859,7 +890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -867,7 +898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -875,7 +906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -883,7 +914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -891,29 +922,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>77</v>
       </c>
       <c r="C20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:O103"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" style="3" customWidth="1"/>
@@ -931,27 +965,27 @@
     <col min="14" max="14" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -959,7 +993,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -967,12 +1001,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -983,7 +1017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -994,12 +1028,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>2</v>
       </c>
@@ -1010,7 +1044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1021,61 +1055,61 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
@@ -1086,7 +1120,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1097,27 +1131,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -1125,7 +1159,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1167,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1141,7 +1175,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1191,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1165,14 +1199,14 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12"/>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>2</v>
       </c>
@@ -1181,7 +1215,7 @@
       </c>
       <c r="C46" s="12"/>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +1224,7 @@
       </c>
       <c r="C47" s="12"/>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1233,7 @@
       </c>
       <c r="C48" s="12"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>3</v>
       </c>
@@ -1208,7 +1242,7 @@
       </c>
       <c r="C49" s="12"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>3</v>
       </c>
@@ -1217,7 +1251,7 @@
       </c>
       <c r="C50" s="12"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1260,7 @@
       </c>
       <c r="C51" s="12"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1268,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>3</v>
       </c>
@@ -1242,7 +1276,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>3</v>
       </c>
@@ -1250,12 +1284,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>2</v>
       </c>
@@ -1266,7 +1300,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>3</v>
       </c>
@@ -1275,7 +1309,7 @@
       </c>
       <c r="C58" s="12"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1318,7 @@
       </c>
       <c r="C59" s="12"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>3</v>
       </c>
@@ -1293,7 +1327,7 @@
       </c>
       <c r="C60" s="12"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>3</v>
       </c>
@@ -1302,7 +1336,7 @@
       </c>
       <c r="C61" s="12"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1345,7 @@
       </c>
       <c r="C62" s="12"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>3</v>
       </c>
@@ -1319,7 +1353,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>3</v>
       </c>
@@ -1327,7 +1361,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>3</v>
       </c>
@@ -1335,7 +1369,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>15</v>
       </c>
@@ -1343,12 +1377,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>2</v>
       </c>
@@ -1395,7 +1429,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="17">
+    <row r="70" spans="1:15" ht="18" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>3</v>
       </c>
@@ -1442,12 +1476,12 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>2</v>
       </c>
@@ -1455,7 +1489,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>3</v>
       </c>
@@ -1463,27 +1497,27 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -1491,7 +1525,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>3</v>
       </c>
@@ -1499,12 +1533,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>2</v>
       </c>
@@ -1512,7 +1546,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="12" t="s">
         <v>3</v>
       </c>
@@ -1520,12 +1554,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="12" t="s">
         <v>2</v>
       </c>
@@ -1533,7 +1567,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="12" t="s">
         <v>3</v>
       </c>
@@ -1541,12 +1575,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="12" t="s">
         <v>2</v>
       </c>
@@ -1554,12 +1588,73 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1571,24 +1666,14 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="25007"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="26311"/>
   <workbookPr filterPrivacy="1" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rumanaafroz/Automation/BaublebarTest/src/com/baublebar/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="14340" yWindow="200" windowWidth="27100" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="23720" yWindow="560" windowWidth="14680" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -21,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="89">
   <si>
     <t>TCID</t>
   </si>
@@ -267,6 +272,27 @@
   </si>
   <si>
     <t>starry-avatar-cuff-bracelet</t>
+  </si>
+  <si>
+    <t>PaginationTest</t>
+  </si>
+  <si>
+    <t>whats-new/just-added</t>
+  </si>
+  <si>
+    <t>necklaces</t>
+  </si>
+  <si>
+    <t>earrings</t>
+  </si>
+  <si>
+    <t>bracelets</t>
+  </si>
+  <si>
+    <t>rings</t>
+  </si>
+  <si>
+    <t>personalized/view-all</t>
   </si>
 </sst>
 </file>
@@ -440,6 +466,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -728,14 +759,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
@@ -755,7 +786,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -763,7 +794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -771,7 +802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -779,7 +810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -787,7 +818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -795,7 +826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -803,7 +834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -811,7 +842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -819,7 +850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -827,7 +858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -835,7 +866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -843,7 +874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -851,7 +882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -859,7 +890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -867,7 +898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -875,7 +906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -883,7 +914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -891,29 +922,32 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>77</v>
       </c>
       <c r="C20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <dimension ref="A1:O103"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" style="3" customWidth="1"/>
@@ -931,27 +965,27 @@
     <col min="14" max="14" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -959,7 +993,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -967,12 +1001,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -983,7 +1017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -994,12 +1028,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>2</v>
       </c>
@@ -1010,7 +1044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -1021,61 +1055,61 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
@@ -1086,7 +1120,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1097,27 +1131,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -1125,7 +1159,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -1133,7 +1167,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>3</v>
       </c>
@@ -1141,7 +1175,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>3</v>
       </c>
@@ -1149,7 +1183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1191,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>3</v>
       </c>
@@ -1165,14 +1199,14 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B45" s="13"/>
       <c r="C45" s="12"/>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>2</v>
       </c>
@@ -1181,7 +1215,7 @@
       </c>
       <c r="C46" s="12"/>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +1224,7 @@
       </c>
       <c r="C47" s="12"/>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>3</v>
       </c>
@@ -1199,7 +1233,7 @@
       </c>
       <c r="C48" s="12"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>3</v>
       </c>
@@ -1208,7 +1242,7 @@
       </c>
       <c r="C49" s="12"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>3</v>
       </c>
@@ -1217,7 +1251,7 @@
       </c>
       <c r="C50" s="12"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1260,7 @@
       </c>
       <c r="C51" s="12"/>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>3</v>
       </c>
@@ -1234,7 +1268,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>3</v>
       </c>
@@ -1242,7 +1276,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>3</v>
       </c>
@@ -1250,12 +1284,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>2</v>
       </c>
@@ -1266,7 +1300,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>3</v>
       </c>
@@ -1275,7 +1309,7 @@
       </c>
       <c r="C58" s="12"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>3</v>
       </c>
@@ -1284,7 +1318,7 @@
       </c>
       <c r="C59" s="12"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>3</v>
       </c>
@@ -1293,7 +1327,7 @@
       </c>
       <c r="C60" s="12"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>3</v>
       </c>
@@ -1302,7 +1336,7 @@
       </c>
       <c r="C61" s="12"/>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1345,7 @@
       </c>
       <c r="C62" s="12"/>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>3</v>
       </c>
@@ -1319,7 +1353,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>3</v>
       </c>
@@ -1327,7 +1361,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
         <v>3</v>
       </c>
@@ -1335,7 +1369,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
         <v>15</v>
       </c>
@@ -1343,12 +1377,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>2</v>
       </c>
@@ -1395,7 +1429,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="17">
+    <row r="70" spans="1:15" ht="18" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>3</v>
       </c>
@@ -1442,12 +1476,12 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>2</v>
       </c>
@@ -1455,7 +1489,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>3</v>
       </c>
@@ -1463,27 +1497,27 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>2</v>
       </c>
@@ -1491,7 +1525,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>3</v>
       </c>
@@ -1499,12 +1533,12 @@
         <v>72</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" s="12" t="s">
         <v>2</v>
       </c>
@@ -1512,7 +1546,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A86" s="12" t="s">
         <v>3</v>
       </c>
@@ -1520,12 +1554,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A89" s="12" t="s">
         <v>2</v>
       </c>
@@ -1533,7 +1567,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A90" s="12" t="s">
         <v>3</v>
       </c>
@@ -1541,12 +1575,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A93" s="12" t="s">
         <v>2</v>
       </c>
@@ -1554,12 +1588,73 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A94" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>2</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1571,24 +1666,14 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
-      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="86">
   <si>
     <t>TCID</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>goldenrod-drops-earrings</t>
+  </si>
+  <si>
+    <t>ContinueShoppingTest</t>
+  </si>
+  <si>
+    <t>pearl-bud-studs-earrings</t>
   </si>
 </sst>
 </file>
@@ -744,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -923,6 +929,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -931,7 +945,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.33203125" customWidth="1"/>
@@ -1608,6 +1622,27 @@
         <v>83</v>
       </c>
     </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>2</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B11" r:id="rId1" display="cmaitri@yahoo.com"/>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="460" windowWidth="20260" windowHeight="15820"/>
+    <workbookView xWindow="1700" yWindow="460" windowWidth="27100" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="104">
   <si>
     <t>TCID</t>
   </si>
@@ -274,61 +274,70 @@
     <t>starry-avatar-cuff-bracelet</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
     <t>VaultPointsWithDiscountTest</t>
   </si>
   <si>
+    <t>bahama-tassel-drops-earrings</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>BBENG</t>
+  </si>
+  <si>
     <t>VaultPointAmount</t>
   </si>
   <si>
     <t>DiscountCode</t>
   </si>
   <si>
-    <t>roma-studs-earrings</t>
-  </si>
-  <si>
-    <t>BBENG</t>
-  </si>
-  <si>
-    <t>AddItemsTest</t>
-  </si>
-  <si>
     <t>PaginationTest</t>
   </si>
   <si>
+    <t>personalized</t>
+  </si>
+  <si>
+    <t>rings</t>
+  </si>
+  <si>
+    <t>earrings</t>
+  </si>
+  <si>
+    <t>bracelets</t>
+  </si>
+  <si>
+    <t>necklaces</t>
+  </si>
+  <si>
+    <t>whats-new/just-added</t>
+  </si>
+  <si>
     <t>RemoveItemFromShoppingCartTest</t>
   </si>
   <si>
     <t>ProductName1</t>
   </si>
   <si>
+    <t>ProductName3</t>
+  </si>
+  <si>
     <t>ProductName2</t>
   </si>
   <si>
-    <t>brunello-studs-earrings</t>
-  </si>
-  <si>
-    <t>whats-new/just-added</t>
-  </si>
-  <si>
-    <t>necklaces</t>
-  </si>
-  <si>
-    <t>earrings</t>
-  </si>
-  <si>
-    <t>bracelets</t>
-  </si>
-  <si>
-    <t>rings</t>
-  </si>
-  <si>
-    <t>personalized/view-all</t>
-  </si>
-  <si>
-    <t>demi-tassel-bib-necklace</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>tundra-drops-earrings</t>
+  </si>
+  <si>
+    <t>tundra-studs-earrings</t>
+  </si>
+  <si>
+    <t>starburst-studs-earrings</t>
   </si>
 </sst>
 </file>
@@ -795,10 +804,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -968,7 +977,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -976,7 +985,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -984,17 +993,9 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1006,13 +1007,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="15.1640625" customWidth="1"/>
@@ -1023,6 +1024,7 @@
     <col min="12" max="12" width="20.1640625" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" customWidth="1"/>
     <col min="14" max="14" width="13.5" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1293,7 +1295,7 @@
       </c>
       <c r="C48" s="12"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>3</v>
       </c>
@@ -1302,7 +1304,7 @@
       </c>
       <c r="C49" s="12"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>3</v>
       </c>
@@ -1311,7 +1313,7 @@
       </c>
       <c r="C50" s="12"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>3</v>
       </c>
@@ -1320,7 +1322,7 @@
       </c>
       <c r="C51" s="12"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
         <v>3</v>
       </c>
@@ -1328,7 +1330,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>3</v>
       </c>
@@ -1336,7 +1338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>3</v>
       </c>
@@ -1344,12 +1346,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>2</v>
       </c>
@@ -1360,7 +1362,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>3</v>
       </c>
@@ -1369,7 +1371,7 @@
       </c>
       <c r="C58" s="12"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>3</v>
       </c>
@@ -1378,7 +1380,7 @@
       </c>
       <c r="C59" s="12"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>3</v>
       </c>
@@ -1387,7 +1389,7 @@
       </c>
       <c r="C60" s="12"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>3</v>
       </c>
@@ -1395,8 +1397,9 @@
         <v>34</v>
       </c>
       <c r="C61" s="12"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>3</v>
       </c>
@@ -1405,7 +1408,7 @@
       </c>
       <c r="C62" s="12"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>3</v>
       </c>
@@ -1413,7 +1416,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>3</v>
       </c>
@@ -1529,11 +1532,11 @@
       <c r="M70" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="N70">
-        <v>12</v>
-      </c>
-      <c r="O70">
-        <v>2019</v>
+      <c r="N70" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
@@ -1658,7 +1661,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
@@ -1666,19 +1669,19 @@
         <v>2</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
         <v>5</v>
       </c>
-      <c r="D97" t="s">
-        <v>45</v>
-      </c>
       <c r="E97" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F97" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -1686,27 +1689,24 @@
         <v>3</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>18</v>
       </c>
-      <c r="D98" t="s">
-        <v>99</v>
-      </c>
       <c r="E98" s="3" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F98" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E99" s="3"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
@@ -1714,10 +1714,7 @@
         <v>2</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C101" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
@@ -1725,39 +1722,47 @@
         <v>3</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C102" t="s">
-        <v>92</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="13" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A104" s="11" t="s">
-        <v>88</v>
+      <c r="A104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>2</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>40</v>
+        <v>3</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>3</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>93</v>
+      <c r="B106" s="13" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
@@ -1765,52 +1770,48 @@
         <v>3</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>3</v>
-      </c>
-      <c r="B110" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>3</v>
-      </c>
-      <c r="B111" s="3" t="s">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>2</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>2</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>85</v>
+      <c r="C112" t="s">
+        <v>100</v>
+      </c>
+      <c r="D112" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C113" t="s">
+        <v>102</v>
+      </c>
+      <c r="D113" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1819,6 +1820,7 @@
     <hyperlink ref="B31" r:id="rId2"/>
     <hyperlink ref="B7" r:id="rId3"/>
     <hyperlink ref="B15" r:id="rId4"/>
+    <hyperlink ref="C98" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293"/>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="460" windowWidth="27100" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="260" yWindow="460" windowWidth="27100" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>tundra-studs-earrings</t>
   </si>
   <si>
-    <t>starburst-studs-earrings</t>
+    <t>roma-studs-earrings</t>
   </si>
 </sst>
 </file>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="460" windowWidth="20260" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="1100" yWindow="460" windowWidth="20260" windowHeight="15820"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="105">
   <si>
     <t>TCID</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>tundra-drops-earrings</t>
+  </si>
+  <si>
+    <t>ContinueShoppingTest</t>
   </si>
 </sst>
 </file>
@@ -804,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -1007,6 +1010,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -1015,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
@@ -1834,6 +1845,27 @@
         <v>103</v>
       </c>
     </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>2</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B11" r:id="rId1" display="cmaitri@yahoo.com"/>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="12040" yWindow="460" windowWidth="14680" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="12040" yWindow="460" windowWidth="14680" windowHeight="15820"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="94">
   <si>
     <t>TCID</t>
   </si>
@@ -277,9 +277,6 @@
     <t>PaginationTest</t>
   </si>
   <si>
-    <t>whats-new/just-added</t>
-  </si>
-  <si>
     <t>necklaces</t>
   </si>
   <si>
@@ -290,12 +287,6 @@
   </si>
   <si>
     <t>rings</t>
-  </si>
-  <si>
-    <t>FilterTest</t>
-  </si>
-  <si>
-    <t>whats-new</t>
   </si>
   <si>
     <t>RemoveItemFromShoppingCartTest</t>
@@ -783,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -964,7 +955,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -972,17 +963,9 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" t="s">
         <v>3</v>
       </c>
     </row>
@@ -994,7 +977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
@@ -1649,7 +1632,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>2</v>
       </c>
@@ -1657,15 +1640,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>3</v>
       </c>
@@ -1673,7 +1656,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>3</v>
       </c>
@@ -1681,7 +1664,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>3</v>
       </c>
@@ -1689,87 +1672,60 @@
         <v>86</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>3</v>
-      </c>
-      <c r="B102" s="3" t="s">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A103" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
+        <v>2</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C104" t="s">
+        <v>89</v>
+      </c>
+      <c r="D104" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="C105" t="s">
+        <v>91</v>
+      </c>
+      <c r="D105" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A107" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>2</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H108" s="15"/>
+      <c r="J108"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C109" t="s">
-        <v>92</v>
-      </c>
-      <c r="D109" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>3</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C110" t="s">
-        <v>94</v>
-      </c>
-      <c r="D110" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>2</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>3</v>
-      </c>
-      <c r="B114" s="3" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="98">
   <si>
     <t>TCID</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>garbo-drops-earrings</t>
+  </si>
+  <si>
+    <t>wishbone-bracelet</t>
   </si>
 </sst>
 </file>
@@ -1103,61 +1106,61 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>3</v>
       </c>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
@@ -1167,8 +1170,11 @@
       <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -1177,6 +1183,9 @@
       </c>
       <c r="C31" s="6" t="s">
         <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="1700" yWindow="460" windowWidth="27100" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="1700" yWindow="460" windowWidth="27100" windowHeight="15820"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -262,9 +262,6 @@
     <t>EarnVaultPointTest</t>
   </si>
   <si>
-    <t>pave-sputnik-ear-jackets-earring</t>
-  </si>
-  <si>
     <t>CCExpirMonth</t>
   </si>
   <si>
@@ -284,6 +281,9 @@
   </si>
   <si>
     <t>roma-studs-earrings</t>
+  </si>
+  <si>
+    <t>bahama-tassel-drops-earrings</t>
   </si>
 </sst>
 </file>
@@ -923,7 +923,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
@@ -1414,10 +1414,10 @@
         <v>65</v>
       </c>
       <c r="N69" t="s">
+        <v>78</v>
+      </c>
+      <c r="O69" t="s">
         <v>79</v>
-      </c>
-      <c r="O69" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:15" ht="18" x14ac:dyDescent="0.2">
@@ -1425,7 +1425,7 @@
         <v>3</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" t="s">
         <v>54</v>
@@ -1485,7 +1485,7 @@
         <v>3</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
@@ -1584,12 +1584,12 @@
         <v>3</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A96" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -1597,10 +1597,10 @@
         <v>2</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C97" t="s">
         <v>83</v>
-      </c>
-      <c r="C97" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -1608,10 +1608,10 @@
         <v>3</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C98" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/src/com/baublebar/data/TestCases.xlsx
+++ b/src/com/baublebar/data/TestCases.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="12040" yWindow="460" windowWidth="14680" windowHeight="15820" activeTab="1"/>
+    <workbookView xWindow="12040" yWindow="460" windowWidth="24240" windowHeight="15820" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="103">
   <si>
     <t>TCID</t>
   </si>
@@ -317,6 +317,24 @@
   </si>
   <si>
     <t>garbo-drops-earrings</t>
+  </si>
+  <si>
+    <t>VerifyColorAndSizeTest</t>
+  </si>
+  <si>
+    <t>pave-eternity-ring</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Clear/Gold</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -783,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -986,6 +1004,14 @@
         <v>3</v>
       </c>
     </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -994,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O114"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.83203125" customWidth="1"/>
@@ -1756,7 +1782,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>2</v>
       </c>
@@ -1764,12 +1790,45 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>3</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>2</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C117" t="s">
+        <v>99</v>
+      </c>
+      <c r="D117" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C118" t="s">
+        <v>100</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
